--- a/RAN_Intelligent_Controllers/research/experiments_7-21-2025/ue_experiments.xlsx
+++ b/RAN_Intelligent_Controllers/research/experiments_7-21-2025/ue_experiments.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\sjw10\Documents\GitHub\AIML\o-ran-testbed-init\RAN_Intelligent_Controllers\research\experiments_7-21-2025\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6AFFF45C-1D39-41AB-A15F-3D09720C8C8D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{263C2EAB-AC7F-494C-8D63-438C0FD1AA1E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="0" windowWidth="11712" windowHeight="13776" xr2:uid="{A0AC0CEE-5452-4B65-B32E-3E025781759E}"/>
+    <workbookView xWindow="8040" yWindow="1260" windowWidth="17280" windowHeight="9960" xr2:uid="{A0AC0CEE-5452-4B65-B32E-3E025781759E}"/>
   </bookViews>
   <sheets>
     <sheet name="ue_experiments" sheetId="1" r:id="rId1"/>
@@ -933,13 +933,13 @@
         <v>0.45049400000000001</v>
       </c>
       <c r="B2">
-        <v>7.1517999999999997</v>
+        <v>6.9550400000000003</v>
       </c>
       <c r="C2">
         <v>0.45049400000000001</v>
       </c>
       <c r="D2">
-        <v>7.1517999999999997</v>
+        <v>6.9550400000000003</v>
       </c>
       <c r="F2" t="s">
         <v>2</v>
@@ -954,20 +954,20 @@
         <v>0.84189400000000003</v>
       </c>
       <c r="B3">
-        <v>10.1625</v>
+        <v>7.2540100000000001</v>
       </c>
       <c r="C3">
         <v>0.84189400000000003</v>
       </c>
       <c r="D3">
-        <v>10.1625</v>
+        <v>7.2540100000000001</v>
       </c>
       <c r="F3" t="s">
         <v>3</v>
       </c>
       <c r="G3" t="str">
         <f>AVERAGE(D2:D101) &amp; " ± " &amp; _xlfn.T.INV(1-(1-0.95)/2, COUNT(D2:D101)-1) * _xlfn.STDEV.S(D2:D101)/SQRT(COUNT(D2:D101))</f>
-        <v>11.1066714 ± 0.311681905026292</v>
+        <v>11.4456073 ± 0.26357268939356</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
@@ -975,13 +975,13 @@
         <v>0.32082699999999997</v>
       </c>
       <c r="B4">
-        <v>13.006</v>
+        <v>13.6716</v>
       </c>
       <c r="C4">
         <v>0.32082699999999997</v>
       </c>
       <c r="D4">
-        <v>13.006</v>
+        <v>13.6716</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
@@ -989,13 +989,13 @@
         <v>0.41988399999999998</v>
       </c>
       <c r="B5">
-        <v>10.228</v>
+        <v>12.2928</v>
       </c>
       <c r="C5">
         <v>0.41988399999999998</v>
       </c>
       <c r="D5">
-        <v>10.228</v>
+        <v>12.2928</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
@@ -1003,13 +1003,13 @@
         <v>0.52854999999999996</v>
       </c>
       <c r="B6">
-        <v>12.724299999999999</v>
+        <v>10.9078</v>
       </c>
       <c r="C6">
         <v>0.52854999999999996</v>
       </c>
       <c r="D6">
-        <v>12.724299999999999</v>
+        <v>10.9078</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
@@ -1017,13 +1017,13 @@
         <v>0.42091899999999999</v>
       </c>
       <c r="B7">
-        <v>10.334</v>
+        <v>10.252800000000001</v>
       </c>
       <c r="C7">
         <v>0.42091899999999999</v>
       </c>
       <c r="D7">
-        <v>10.334</v>
+        <v>10.252800000000001</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
@@ -1031,13 +1031,13 @@
         <v>0.419572</v>
       </c>
       <c r="B8">
-        <v>12.1374</v>
+        <v>12.3483</v>
       </c>
       <c r="C8">
         <v>0.419572</v>
       </c>
       <c r="D8">
-        <v>12.1374</v>
+        <v>12.3483</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -1045,13 +1045,13 @@
         <v>0.31551499999999999</v>
       </c>
       <c r="B9">
-        <v>7.1587300000000003</v>
+        <v>10.5351</v>
       </c>
       <c r="C9">
         <v>0.31551499999999999</v>
       </c>
       <c r="D9">
-        <v>7.1587300000000003</v>
+        <v>10.5351</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
@@ -1059,13 +1059,13 @@
         <v>0.43018400000000001</v>
       </c>
       <c r="B10">
-        <v>11.505800000000001</v>
+        <v>12.2256</v>
       </c>
       <c r="C10">
         <v>0.43018400000000001</v>
       </c>
       <c r="D10">
-        <v>11.505800000000001</v>
+        <v>12.2256</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -1073,13 +1073,13 @@
         <v>0.31912099999999999</v>
       </c>
       <c r="B11">
-        <v>10.3569</v>
+        <v>12.1721</v>
       </c>
       <c r="C11">
         <v>0.31912099999999999</v>
       </c>
       <c r="D11">
-        <v>10.3569</v>
+        <v>12.1721</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
@@ -1087,13 +1087,13 @@
         <v>0.31950400000000001</v>
       </c>
       <c r="B12">
-        <v>9.8903999999999996</v>
+        <v>11.906700000000001</v>
       </c>
       <c r="C12">
         <v>0.31950400000000001</v>
       </c>
       <c r="D12">
-        <v>9.8903999999999996</v>
+        <v>11.906700000000001</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
@@ -1101,13 +1101,13 @@
         <v>0.42327500000000001</v>
       </c>
       <c r="B13">
-        <v>9.8823799999999995</v>
+        <v>12.2197</v>
       </c>
       <c r="C13">
         <v>0.42327500000000001</v>
       </c>
       <c r="D13">
-        <v>9.8823799999999995</v>
+        <v>12.2197</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -1115,13 +1115,13 @@
         <v>0.31641399999999997</v>
       </c>
       <c r="B14">
-        <v>10.8165</v>
+        <v>12.3454</v>
       </c>
       <c r="C14">
         <v>0.31641399999999997</v>
       </c>
       <c r="D14">
-        <v>10.8165</v>
+        <v>12.3454</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
@@ -1129,13 +1129,13 @@
         <v>0.42369000000000001</v>
       </c>
       <c r="B15">
-        <v>10.8781</v>
+        <v>12.0139</v>
       </c>
       <c r="C15">
         <v>0.42369000000000001</v>
       </c>
       <c r="D15">
-        <v>10.8781</v>
+        <v>12.0139</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
@@ -1143,13 +1143,13 @@
         <v>0.42087200000000002</v>
       </c>
       <c r="B16">
-        <v>10.2463</v>
+        <v>11.8148</v>
       </c>
       <c r="C16">
         <v>0.42087200000000002</v>
       </c>
       <c r="D16">
-        <v>10.2463</v>
+        <v>11.8148</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.3">
@@ -1157,13 +1157,13 @@
         <v>0.42175099999999999</v>
       </c>
       <c r="B17">
-        <v>12.1569</v>
+        <v>12.067500000000001</v>
       </c>
       <c r="C17">
         <v>0.42175099999999999</v>
       </c>
       <c r="D17">
-        <v>12.1569</v>
+        <v>12.067500000000001</v>
       </c>
     </row>
     <row r="18" spans="1:4" x14ac:dyDescent="0.3">
@@ -1171,13 +1171,13 @@
         <v>0.42128300000000002</v>
       </c>
       <c r="B18">
-        <v>12.090999999999999</v>
+        <v>12.4818</v>
       </c>
       <c r="C18">
         <v>0.42128300000000002</v>
       </c>
       <c r="D18">
-        <v>12.090999999999999</v>
+        <v>12.4818</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.3">
@@ -1185,13 +1185,13 @@
         <v>0.42124400000000001</v>
       </c>
       <c r="B19">
-        <v>8.1158199999999994</v>
+        <v>10.2051</v>
       </c>
       <c r="C19">
         <v>0.42124400000000001</v>
       </c>
       <c r="D19">
-        <v>8.1158199999999994</v>
+        <v>10.2051</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.3">
@@ -1199,13 +1199,13 @@
         <v>0.42363800000000001</v>
       </c>
       <c r="B20">
-        <v>12.114000000000001</v>
+        <v>12.4453</v>
       </c>
       <c r="C20">
         <v>0.42363800000000001</v>
       </c>
       <c r="D20">
-        <v>12.114000000000001</v>
+        <v>12.4453</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.3">
@@ -1213,13 +1213,13 @@
         <v>0.42662499999999998</v>
       </c>
       <c r="B21">
-        <v>10.0236</v>
+        <v>10.5352</v>
       </c>
       <c r="C21">
         <v>0.42662499999999998</v>
       </c>
       <c r="D21">
-        <v>10.0236</v>
+        <v>10.5352</v>
       </c>
     </row>
     <row r="22" spans="1:4" x14ac:dyDescent="0.3">
@@ -1227,13 +1227,13 @@
         <v>0.31710300000000002</v>
       </c>
       <c r="B22">
-        <v>12.0443</v>
+        <v>12.170299999999999</v>
       </c>
       <c r="C22">
         <v>0.31710300000000002</v>
       </c>
       <c r="D22">
-        <v>12.0443</v>
+        <v>12.170299999999999</v>
       </c>
     </row>
     <row r="23" spans="1:4" x14ac:dyDescent="0.3">
@@ -1241,13 +1241,13 @@
         <v>0.42093199999999997</v>
       </c>
       <c r="B23">
-        <v>13.035500000000001</v>
+        <v>12.565300000000001</v>
       </c>
       <c r="C23">
         <v>0.42093199999999997</v>
       </c>
       <c r="D23">
-        <v>13.035500000000001</v>
+        <v>12.565300000000001</v>
       </c>
     </row>
     <row r="24" spans="1:4" x14ac:dyDescent="0.3">
@@ -1255,13 +1255,13 @@
         <v>0.42271799999999998</v>
       </c>
       <c r="B24">
-        <v>11.621700000000001</v>
+        <v>12.057600000000001</v>
       </c>
       <c r="C24">
         <v>0.42271799999999998</v>
       </c>
       <c r="D24">
-        <v>11.621700000000001</v>
+        <v>12.057600000000001</v>
       </c>
     </row>
     <row r="25" spans="1:4" x14ac:dyDescent="0.3">
@@ -1269,13 +1269,13 @@
         <v>0.42246299999999998</v>
       </c>
       <c r="B25">
-        <v>11.922000000000001</v>
+        <v>7.5921900000000004</v>
       </c>
       <c r="C25">
         <v>0.42246299999999998</v>
       </c>
       <c r="D25">
-        <v>11.922000000000001</v>
+        <v>7.5921900000000004</v>
       </c>
     </row>
     <row r="26" spans="1:4" x14ac:dyDescent="0.3">
@@ -1283,13 +1283,13 @@
         <v>0.42119899999999999</v>
       </c>
       <c r="B26">
-        <v>12.117900000000001</v>
+        <v>9.9031099999999999</v>
       </c>
       <c r="C26">
         <v>0.42119899999999999</v>
       </c>
       <c r="D26">
-        <v>12.117900000000001</v>
+        <v>9.9031099999999999</v>
       </c>
     </row>
     <row r="27" spans="1:4" x14ac:dyDescent="0.3">
@@ -1297,13 +1297,13 @@
         <v>0.42242200000000002</v>
       </c>
       <c r="B27">
-        <v>12.56</v>
+        <v>12.960900000000001</v>
       </c>
       <c r="C27">
         <v>0.42242200000000002</v>
       </c>
       <c r="D27">
-        <v>12.56</v>
+        <v>12.960900000000001</v>
       </c>
     </row>
     <row r="28" spans="1:4" x14ac:dyDescent="0.3">
@@ -1311,13 +1311,13 @@
         <v>0.337059</v>
       </c>
       <c r="B28">
-        <v>12.412800000000001</v>
+        <v>12.210900000000001</v>
       </c>
       <c r="C28">
         <v>0.337059</v>
       </c>
       <c r="D28">
-        <v>12.412800000000001</v>
+        <v>12.210900000000001</v>
       </c>
     </row>
     <row r="29" spans="1:4" x14ac:dyDescent="0.3">
@@ -1325,13 +1325,13 @@
         <v>0.31842199999999998</v>
       </c>
       <c r="B29">
-        <v>12.620100000000001</v>
+        <v>11.9063</v>
       </c>
       <c r="C29">
         <v>0.31842199999999998</v>
       </c>
       <c r="D29">
-        <v>12.620100000000001</v>
+        <v>11.9063</v>
       </c>
     </row>
     <row r="30" spans="1:4" x14ac:dyDescent="0.3">
@@ -1339,13 +1339,13 @@
         <v>0.42472399999999999</v>
       </c>
       <c r="B30">
-        <v>9.8566599999999998</v>
+        <v>11.884600000000001</v>
       </c>
       <c r="C30">
         <v>0.42472399999999999</v>
       </c>
       <c r="D30">
-        <v>9.8566599999999998</v>
+        <v>11.884600000000001</v>
       </c>
     </row>
     <row r="31" spans="1:4" x14ac:dyDescent="0.3">
@@ -1353,13 +1353,13 @@
         <v>0.52400599999999997</v>
       </c>
       <c r="B31">
-        <v>9.7496299999999998</v>
+        <v>10.227499999999999</v>
       </c>
       <c r="C31">
         <v>0.52400599999999997</v>
       </c>
       <c r="D31">
-        <v>9.7496299999999998</v>
+        <v>10.227499999999999</v>
       </c>
     </row>
     <row r="32" spans="1:4" x14ac:dyDescent="0.3">
@@ -1367,13 +1367,13 @@
         <v>0.418993</v>
       </c>
       <c r="B32">
-        <v>12.353899999999999</v>
+        <v>10.1144</v>
       </c>
       <c r="C32">
         <v>0.418993</v>
       </c>
       <c r="D32">
-        <v>12.353899999999999</v>
+        <v>10.1144</v>
       </c>
     </row>
     <row r="33" spans="1:4" x14ac:dyDescent="0.3">
@@ -1381,13 +1381,13 @@
         <v>0.42107099999999997</v>
       </c>
       <c r="B33">
-        <v>12.2905</v>
+        <v>11.0174</v>
       </c>
       <c r="C33">
         <v>0.42107099999999997</v>
       </c>
       <c r="D33">
-        <v>12.2905</v>
+        <v>11.0174</v>
       </c>
     </row>
     <row r="34" spans="1:4" x14ac:dyDescent="0.3">
@@ -1395,13 +1395,13 @@
         <v>0.421379</v>
       </c>
       <c r="B34">
-        <v>11.997199999999999</v>
+        <v>12.641400000000001</v>
       </c>
       <c r="C34">
         <v>0.421379</v>
       </c>
       <c r="D34">
-        <v>11.997199999999999</v>
+        <v>12.641400000000001</v>
       </c>
     </row>
     <row r="35" spans="1:4" x14ac:dyDescent="0.3">
@@ -1409,13 +1409,13 @@
         <v>0.52518200000000004</v>
       </c>
       <c r="B35">
-        <v>10.2422</v>
+        <v>12.566599999999999</v>
       </c>
       <c r="C35">
         <v>0.52518200000000004</v>
       </c>
       <c r="D35">
-        <v>10.2422</v>
+        <v>12.566599999999999</v>
       </c>
     </row>
     <row r="36" spans="1:4" x14ac:dyDescent="0.3">
@@ -1423,13 +1423,13 @@
         <v>0.42052299999999998</v>
       </c>
       <c r="B36">
-        <v>9.9141700000000004</v>
+        <v>10.165900000000001</v>
       </c>
       <c r="C36">
         <v>0.42052299999999998</v>
       </c>
       <c r="D36">
-        <v>9.9141700000000004</v>
+        <v>10.165900000000001</v>
       </c>
     </row>
     <row r="37" spans="1:4" x14ac:dyDescent="0.3">
@@ -1437,13 +1437,13 @@
         <v>0.42297099999999999</v>
       </c>
       <c r="B37">
-        <v>10.467000000000001</v>
+        <v>12.443</v>
       </c>
       <c r="C37">
         <v>0.42297099999999999</v>
       </c>
       <c r="D37">
-        <v>10.467000000000001</v>
+        <v>12.443</v>
       </c>
     </row>
     <row r="38" spans="1:4" x14ac:dyDescent="0.3">
@@ -1451,13 +1451,13 @@
         <v>0.42231299999999999</v>
       </c>
       <c r="B38">
-        <v>7.1101599999999996</v>
+        <v>12.2843</v>
       </c>
       <c r="C38">
         <v>0.42231299999999999</v>
       </c>
       <c r="D38">
-        <v>7.1101599999999996</v>
+        <v>12.2843</v>
       </c>
     </row>
     <row r="39" spans="1:4" x14ac:dyDescent="0.3">
@@ -1465,13 +1465,13 @@
         <v>0.42054000000000002</v>
       </c>
       <c r="B39">
-        <v>12.4816</v>
+        <v>12.5616</v>
       </c>
       <c r="C39">
         <v>0.42054000000000002</v>
       </c>
       <c r="D39">
-        <v>12.4816</v>
+        <v>12.5616</v>
       </c>
     </row>
     <row r="40" spans="1:4" x14ac:dyDescent="0.3">
@@ -1479,13 +1479,13 @@
         <v>0.42118</v>
       </c>
       <c r="B40">
-        <v>7.16561</v>
+        <v>12.3424</v>
       </c>
       <c r="C40">
         <v>0.42118</v>
       </c>
       <c r="D40">
-        <v>7.16561</v>
+        <v>12.3424</v>
       </c>
     </row>
     <row r="41" spans="1:4" x14ac:dyDescent="0.3">
@@ -1493,13 +1493,13 @@
         <v>0.42196099999999997</v>
       </c>
       <c r="B41">
-        <v>10.045500000000001</v>
+        <v>10.5633</v>
       </c>
       <c r="C41">
         <v>0.42196099999999997</v>
       </c>
       <c r="D41">
-        <v>10.045500000000001</v>
+        <v>10.5633</v>
       </c>
     </row>
     <row r="42" spans="1:4" x14ac:dyDescent="0.3">
@@ -1507,13 +1507,13 @@
         <v>0.31723200000000001</v>
       </c>
       <c r="B42">
-        <v>12.3027</v>
+        <v>11.926299999999999</v>
       </c>
       <c r="C42">
         <v>0.31723200000000001</v>
       </c>
       <c r="D42">
-        <v>12.3027</v>
+        <v>11.926299999999999</v>
       </c>
     </row>
     <row r="43" spans="1:4" x14ac:dyDescent="0.3">
@@ -1521,13 +1521,13 @@
         <v>0.42444599999999999</v>
       </c>
       <c r="B43">
-        <v>9.77379</v>
+        <v>11.9267</v>
       </c>
       <c r="C43">
         <v>0.42444599999999999</v>
       </c>
       <c r="D43">
-        <v>9.77379</v>
+        <v>11.9267</v>
       </c>
     </row>
     <row r="44" spans="1:4" x14ac:dyDescent="0.3">
@@ -1535,13 +1535,13 @@
         <v>0.41821900000000001</v>
       </c>
       <c r="B44">
-        <v>11.889200000000001</v>
+        <v>12.348699999999999</v>
       </c>
       <c r="C44">
         <v>0.41821900000000001</v>
       </c>
       <c r="D44">
-        <v>11.889200000000001</v>
+        <v>12.348699999999999</v>
       </c>
     </row>
     <row r="45" spans="1:4" x14ac:dyDescent="0.3">
@@ -1549,13 +1549,13 @@
         <v>0.425981</v>
       </c>
       <c r="B45">
-        <v>12.7203</v>
+        <v>12.4503</v>
       </c>
       <c r="C45">
         <v>0.425981</v>
       </c>
       <c r="D45">
-        <v>12.7203</v>
+        <v>12.4503</v>
       </c>
     </row>
     <row r="46" spans="1:4" x14ac:dyDescent="0.3">
@@ -1563,13 +1563,13 @@
         <v>0.424792</v>
       </c>
       <c r="B46">
-        <v>12.7216</v>
+        <v>12.354200000000001</v>
       </c>
       <c r="C46">
         <v>0.424792</v>
       </c>
       <c r="D46">
-        <v>12.7216</v>
+        <v>12.354200000000001</v>
       </c>
     </row>
     <row r="47" spans="1:4" x14ac:dyDescent="0.3">
@@ -1577,13 +1577,13 @@
         <v>0.41933700000000002</v>
       </c>
       <c r="B47">
-        <v>10.1601</v>
+        <v>6.9687200000000002</v>
       </c>
       <c r="C47">
         <v>0.41933700000000002</v>
       </c>
       <c r="D47">
-        <v>10.1601</v>
+        <v>6.9687200000000002</v>
       </c>
     </row>
     <row r="48" spans="1:4" x14ac:dyDescent="0.3">
@@ -1591,13 +1591,13 @@
         <v>0.42246099999999998</v>
       </c>
       <c r="B48">
-        <v>11.8421</v>
+        <v>10.212199999999999</v>
       </c>
       <c r="C48">
         <v>0.42246099999999998</v>
       </c>
       <c r="D48">
-        <v>11.8421</v>
+        <v>10.212199999999999</v>
       </c>
     </row>
     <row r="49" spans="1:4" x14ac:dyDescent="0.3">
@@ -1605,13 +1605,13 @@
         <v>0.42220299999999999</v>
       </c>
       <c r="B49">
-        <v>10.464700000000001</v>
+        <v>12.2674</v>
       </c>
       <c r="C49">
         <v>0.42220299999999999</v>
       </c>
       <c r="D49">
-        <v>10.464700000000001</v>
+        <v>12.2674</v>
       </c>
     </row>
     <row r="50" spans="1:4" x14ac:dyDescent="0.3">
@@ -1619,13 +1619,13 @@
         <v>0.42143199999999997</v>
       </c>
       <c r="B50">
-        <v>12.289199999999999</v>
+        <v>10.160299999999999</v>
       </c>
       <c r="C50">
         <v>0.42143199999999997</v>
       </c>
       <c r="D50">
-        <v>12.289199999999999</v>
+        <v>10.160299999999999</v>
       </c>
     </row>
     <row r="51" spans="1:4" x14ac:dyDescent="0.3">
@@ -1633,13 +1633,13 @@
         <v>0.31561099999999997</v>
       </c>
       <c r="B51">
-        <v>10.4344</v>
+        <v>12.298299999999999</v>
       </c>
       <c r="C51">
         <v>0.31561099999999997</v>
       </c>
       <c r="D51">
-        <v>10.4344</v>
+        <v>12.298299999999999</v>
       </c>
     </row>
     <row r="52" spans="1:4" x14ac:dyDescent="0.3">
@@ -1647,13 +1647,13 @@
         <v>0.42230499999999999</v>
       </c>
       <c r="B52">
-        <v>10.351699999999999</v>
+        <v>10.414400000000001</v>
       </c>
       <c r="C52">
         <v>0.42230499999999999</v>
       </c>
       <c r="D52">
-        <v>10.351699999999999</v>
+        <v>10.414400000000001</v>
       </c>
     </row>
     <row r="53" spans="1:4" x14ac:dyDescent="0.3">
@@ -1661,13 +1661,13 @@
         <v>0.42511199999999999</v>
       </c>
       <c r="B53">
-        <v>12.523199999999999</v>
+        <v>12.7273</v>
       </c>
       <c r="C53">
         <v>0.42511199999999999</v>
       </c>
       <c r="D53">
-        <v>12.523199999999999</v>
+        <v>12.7273</v>
       </c>
     </row>
     <row r="54" spans="1:4" x14ac:dyDescent="0.3">
@@ -1675,13 +1675,13 @@
         <v>0.41914899999999999</v>
       </c>
       <c r="B54">
-        <v>12.120200000000001</v>
+        <v>10.3482</v>
       </c>
       <c r="C54">
         <v>0.41914899999999999</v>
       </c>
       <c r="D54">
-        <v>12.120200000000001</v>
+        <v>10.3482</v>
       </c>
     </row>
     <row r="55" spans="1:4" x14ac:dyDescent="0.3">
@@ -1689,13 +1689,13 @@
         <v>0.42289199999999999</v>
       </c>
       <c r="B55">
-        <v>11.798500000000001</v>
+        <v>12.319599999999999</v>
       </c>
       <c r="C55">
         <v>0.42289199999999999</v>
       </c>
       <c r="D55">
-        <v>11.798500000000001</v>
+        <v>12.319599999999999</v>
       </c>
     </row>
     <row r="56" spans="1:4" x14ac:dyDescent="0.3">
@@ -1703,13 +1703,13 @@
         <v>0.42272999999999999</v>
       </c>
       <c r="B56">
-        <v>9.8618000000000006</v>
+        <v>12.2357</v>
       </c>
       <c r="C56">
         <v>0.42272999999999999</v>
       </c>
       <c r="D56">
-        <v>9.8618000000000006</v>
+        <v>12.2357</v>
       </c>
     </row>
     <row r="57" spans="1:4" x14ac:dyDescent="0.3">
@@ -1717,13 +1717,13 @@
         <v>0.42272900000000002</v>
       </c>
       <c r="B57">
-        <v>12.6791</v>
+        <v>9.6395900000000001</v>
       </c>
       <c r="C57">
         <v>0.42272900000000002</v>
       </c>
       <c r="D57">
-        <v>12.6791</v>
+        <v>9.6395900000000001</v>
       </c>
     </row>
     <row r="58" spans="1:4" x14ac:dyDescent="0.3">
@@ -1731,13 +1731,13 @@
         <v>0.42403000000000002</v>
       </c>
       <c r="B58">
-        <v>10.5328</v>
+        <v>11.845800000000001</v>
       </c>
       <c r="C58">
         <v>0.42403000000000002</v>
       </c>
       <c r="D58">
-        <v>10.5328</v>
+        <v>11.845800000000001</v>
       </c>
     </row>
     <row r="59" spans="1:4" x14ac:dyDescent="0.3">
@@ -1745,13 +1745,13 @@
         <v>0.31648900000000002</v>
       </c>
       <c r="B59">
-        <v>12.530099999999999</v>
+        <v>12.563000000000001</v>
       </c>
       <c r="C59">
         <v>0.31648900000000002</v>
       </c>
       <c r="D59">
-        <v>12.530099999999999</v>
+        <v>12.563000000000001</v>
       </c>
     </row>
     <row r="60" spans="1:4" x14ac:dyDescent="0.3">
@@ -1759,13 +1759,13 @@
         <v>0.31711299999999998</v>
       </c>
       <c r="B60">
-        <v>10.0777</v>
+        <v>10.5182</v>
       </c>
       <c r="C60">
         <v>0.31711299999999998</v>
       </c>
       <c r="D60">
-        <v>10.0777</v>
+        <v>10.5182</v>
       </c>
     </row>
     <row r="61" spans="1:4" x14ac:dyDescent="0.3">
@@ -1773,13 +1773,13 @@
         <v>0.422676</v>
       </c>
       <c r="B61">
-        <v>12.2433</v>
+        <v>11.9907</v>
       </c>
       <c r="C61">
         <v>0.422676</v>
       </c>
       <c r="D61">
-        <v>12.2433</v>
+        <v>11.9907</v>
       </c>
     </row>
     <row r="62" spans="1:4" x14ac:dyDescent="0.3">
@@ -1787,13 +1787,13 @@
         <v>0.424763</v>
       </c>
       <c r="B62">
-        <v>12.4374</v>
+        <v>12.4648</v>
       </c>
       <c r="C62">
         <v>0.424763</v>
       </c>
       <c r="D62">
-        <v>12.4374</v>
+        <v>12.4648</v>
       </c>
     </row>
     <row r="63" spans="1:4" x14ac:dyDescent="0.3">
@@ -1801,13 +1801,13 @@
         <v>0.31740000000000002</v>
       </c>
       <c r="B63">
-        <v>10.407500000000001</v>
+        <v>10.373200000000001</v>
       </c>
       <c r="C63">
         <v>0.31740000000000002</v>
       </c>
       <c r="D63">
-        <v>10.407500000000001</v>
+        <v>10.373200000000001</v>
       </c>
     </row>
     <row r="64" spans="1:4" x14ac:dyDescent="0.3">
@@ -1815,13 +1815,13 @@
         <v>0.20965900000000001</v>
       </c>
       <c r="B64">
-        <v>12.5923</v>
+        <v>12.513400000000001</v>
       </c>
       <c r="C64">
         <v>0.20965900000000001</v>
       </c>
       <c r="D64">
-        <v>12.5923</v>
+        <v>12.513400000000001</v>
       </c>
     </row>
     <row r="65" spans="1:4" x14ac:dyDescent="0.3">
@@ -1829,13 +1829,13 @@
         <v>0.212474</v>
       </c>
       <c r="B65">
-        <v>7.1147900000000002</v>
+        <v>9.9214300000000009</v>
       </c>
       <c r="C65">
         <v>0.212474</v>
       </c>
       <c r="D65">
-        <v>7.1147900000000002</v>
+        <v>9.9214300000000009</v>
       </c>
     </row>
     <row r="66" spans="1:4" x14ac:dyDescent="0.3">
@@ -1843,13 +1843,13 @@
         <v>0.31734099999999998</v>
       </c>
       <c r="B66">
-        <v>12.029199999999999</v>
+        <v>11.742599999999999</v>
       </c>
       <c r="C66">
         <v>0.31734099999999998</v>
       </c>
       <c r="D66">
-        <v>12.029199999999999</v>
+        <v>11.742599999999999</v>
       </c>
     </row>
     <row r="67" spans="1:4" x14ac:dyDescent="0.3">
@@ -1857,13 +1857,13 @@
         <v>0.31839899999999999</v>
       </c>
       <c r="B67">
-        <v>12.511799999999999</v>
+        <v>12.2529</v>
       </c>
       <c r="C67">
         <v>0.31839899999999999</v>
       </c>
       <c r="D67">
-        <v>12.511799999999999</v>
+        <v>12.2529</v>
       </c>
     </row>
     <row r="68" spans="1:4" x14ac:dyDescent="0.3">
@@ -1871,13 +1871,13 @@
         <v>0.42159000000000002</v>
       </c>
       <c r="B68">
-        <v>12.3931</v>
+        <v>12.411300000000001</v>
       </c>
       <c r="C68">
         <v>0.42159000000000002</v>
       </c>
       <c r="D68">
-        <v>12.3931</v>
+        <v>12.411300000000001</v>
       </c>
     </row>
     <row r="69" spans="1:4" x14ac:dyDescent="0.3">
@@ -1885,13 +1885,13 @@
         <v>0.316525</v>
       </c>
       <c r="B69">
-        <v>10.3147</v>
+        <v>12.3203</v>
       </c>
       <c r="C69">
         <v>0.316525</v>
       </c>
       <c r="D69">
-        <v>10.3147</v>
+        <v>12.3203</v>
       </c>
     </row>
     <row r="70" spans="1:4" x14ac:dyDescent="0.3">
@@ -1899,13 +1899,13 @@
         <v>0.315724</v>
       </c>
       <c r="B70">
-        <v>7.5365599999999997</v>
+        <v>12.5753</v>
       </c>
       <c r="C70">
         <v>0.315724</v>
       </c>
       <c r="D70">
-        <v>7.5365599999999997</v>
+        <v>12.5753</v>
       </c>
     </row>
     <row r="71" spans="1:4" x14ac:dyDescent="0.3">
@@ -1913,13 +1913,13 @@
         <v>0.42161700000000002</v>
       </c>
       <c r="B71">
-        <v>11.8963</v>
+        <v>12.140700000000001</v>
       </c>
       <c r="C71">
         <v>0.42161700000000002</v>
       </c>
       <c r="D71">
-        <v>11.8963</v>
+        <v>12.140700000000001</v>
       </c>
     </row>
     <row r="72" spans="1:4" x14ac:dyDescent="0.3">
@@ -1927,13 +1927,13 @@
         <v>0.42139300000000002</v>
       </c>
       <c r="B72">
-        <v>11.6973</v>
+        <v>12.991899999999999</v>
       </c>
       <c r="C72">
         <v>0.42139300000000002</v>
       </c>
       <c r="D72">
-        <v>11.6973</v>
+        <v>12.991899999999999</v>
       </c>
     </row>
     <row r="73" spans="1:4" x14ac:dyDescent="0.3">
@@ -1941,13 +1941,13 @@
         <v>0.42108000000000001</v>
       </c>
       <c r="B73">
-        <v>12.24</v>
+        <v>12.4398</v>
       </c>
       <c r="C73">
         <v>0.42108000000000001</v>
       </c>
       <c r="D73">
-        <v>12.24</v>
+        <v>12.4398</v>
       </c>
     </row>
     <row r="74" spans="1:4" x14ac:dyDescent="0.3">
@@ -1955,13 +1955,13 @@
         <v>0.31544800000000001</v>
       </c>
       <c r="B74">
-        <v>9.6572499999999994</v>
+        <v>12.308999999999999</v>
       </c>
       <c r="C74">
         <v>0.31544800000000001</v>
       </c>
       <c r="D74">
-        <v>9.6572499999999994</v>
+        <v>12.308999999999999</v>
       </c>
     </row>
     <row r="75" spans="1:4" x14ac:dyDescent="0.3">
@@ -1969,13 +1969,13 @@
         <v>0.42264600000000002</v>
       </c>
       <c r="B75">
-        <v>7.1210199999999997</v>
+        <v>10.653600000000001</v>
       </c>
       <c r="C75">
         <v>0.42264600000000002</v>
       </c>
       <c r="D75">
-        <v>7.1210199999999997</v>
+        <v>10.653600000000001</v>
       </c>
     </row>
     <row r="76" spans="1:4" x14ac:dyDescent="0.3">
@@ -1983,13 +1983,13 @@
         <v>0.41930800000000001</v>
       </c>
       <c r="B76">
-        <v>12.0288</v>
+        <v>11.8477</v>
       </c>
       <c r="C76">
         <v>0.41930800000000001</v>
       </c>
       <c r="D76">
-        <v>12.0288</v>
+        <v>11.8477</v>
       </c>
     </row>
     <row r="77" spans="1:4" x14ac:dyDescent="0.3">
@@ -1997,13 +1997,13 @@
         <v>0.42314800000000002</v>
       </c>
       <c r="B77">
-        <v>6.9635699999999998</v>
+        <v>9.7547800000000002</v>
       </c>
       <c r="C77">
         <v>0.42314800000000002</v>
       </c>
       <c r="D77">
-        <v>6.9635699999999998</v>
+        <v>9.7547800000000002</v>
       </c>
     </row>
     <row r="78" spans="1:4" x14ac:dyDescent="0.3">
@@ -2011,13 +2011,13 @@
         <v>0.326623</v>
       </c>
       <c r="B78">
-        <v>12.1206</v>
+        <v>10.0184</v>
       </c>
       <c r="C78">
         <v>0.326623</v>
       </c>
       <c r="D78">
-        <v>12.1206</v>
+        <v>10.0184</v>
       </c>
     </row>
     <row r="79" spans="1:4" x14ac:dyDescent="0.3">
@@ -2025,13 +2025,13 @@
         <v>0.423682</v>
       </c>
       <c r="B79">
-        <v>12.099600000000001</v>
+        <v>12.114599999999999</v>
       </c>
       <c r="C79">
         <v>0.423682</v>
       </c>
       <c r="D79">
-        <v>12.099600000000001</v>
+        <v>12.114599999999999</v>
       </c>
     </row>
     <row r="80" spans="1:4" x14ac:dyDescent="0.3">
@@ -2039,13 +2039,13 @@
         <v>0.42422199999999999</v>
       </c>
       <c r="B80">
-        <v>12.228199999999999</v>
+        <v>12.727600000000001</v>
       </c>
       <c r="C80">
         <v>0.42422199999999999</v>
       </c>
       <c r="D80">
-        <v>12.228199999999999</v>
+        <v>12.727600000000001</v>
       </c>
     </row>
     <row r="81" spans="1:4" x14ac:dyDescent="0.3">
@@ -2053,13 +2053,13 @@
         <v>0.63127299999999997</v>
       </c>
       <c r="B81">
-        <v>9.4981000000000009</v>
+        <v>12.394</v>
       </c>
       <c r="C81">
         <v>0.63127299999999997</v>
       </c>
       <c r="D81">
-        <v>9.4981000000000009</v>
+        <v>12.394</v>
       </c>
     </row>
     <row r="82" spans="1:4" x14ac:dyDescent="0.3">
@@ -2067,13 +2067,13 @@
         <v>0.41980899999999999</v>
       </c>
       <c r="B82">
-        <v>11.7174</v>
+        <v>10.2546</v>
       </c>
       <c r="C82">
         <v>0.41980899999999999</v>
       </c>
       <c r="D82">
-        <v>11.7174</v>
+        <v>10.2546</v>
       </c>
     </row>
     <row r="83" spans="1:4" x14ac:dyDescent="0.3">
@@ -2081,13 +2081,13 @@
         <v>0.41875200000000001</v>
       </c>
       <c r="B83">
-        <v>12.3476</v>
+        <v>12.061199999999999</v>
       </c>
       <c r="C83">
         <v>0.41875200000000001</v>
       </c>
       <c r="D83">
-        <v>12.3476</v>
+        <v>12.061199999999999</v>
       </c>
     </row>
     <row r="84" spans="1:4" x14ac:dyDescent="0.3">
@@ -2095,13 +2095,13 @@
         <v>0.421182</v>
       </c>
       <c r="B84">
-        <v>11.8758</v>
+        <v>12.4528</v>
       </c>
       <c r="C84">
         <v>0.421182</v>
       </c>
       <c r="D84">
-        <v>11.8758</v>
+        <v>12.4528</v>
       </c>
     </row>
     <row r="85" spans="1:4" x14ac:dyDescent="0.3">
@@ -2109,13 +2109,13 @@
         <v>0.42274699999999998</v>
       </c>
       <c r="B85">
-        <v>10.045199999999999</v>
+        <v>10.0977</v>
       </c>
       <c r="C85">
         <v>0.42274699999999998</v>
       </c>
       <c r="D85">
-        <v>10.045199999999999</v>
+        <v>10.0977</v>
       </c>
     </row>
     <row r="86" spans="1:4" x14ac:dyDescent="0.3">
@@ -2123,13 +2123,13 @@
         <v>0.52381599999999995</v>
       </c>
       <c r="B86">
-        <v>12.036099999999999</v>
+        <v>9.7246100000000002</v>
       </c>
       <c r="C86">
         <v>0.52381599999999995</v>
       </c>
       <c r="D86">
-        <v>12.036099999999999</v>
+        <v>9.7246100000000002</v>
       </c>
     </row>
     <row r="87" spans="1:4" x14ac:dyDescent="0.3">
@@ -2137,13 +2137,13 @@
         <v>0.42228500000000002</v>
       </c>
       <c r="B87">
-        <v>12.147600000000001</v>
+        <v>12.107100000000001</v>
       </c>
       <c r="C87">
         <v>0.42228500000000002</v>
       </c>
       <c r="D87">
-        <v>12.147600000000001</v>
+        <v>12.107100000000001</v>
       </c>
     </row>
     <row r="88" spans="1:4" x14ac:dyDescent="0.3">
@@ -2151,13 +2151,13 @@
         <v>0.42610599999999998</v>
       </c>
       <c r="B88">
-        <v>11.704000000000001</v>
+        <v>10.8553</v>
       </c>
       <c r="C88">
         <v>0.42610599999999998</v>
       </c>
       <c r="D88">
-        <v>11.704000000000001</v>
+        <v>10.8553</v>
       </c>
     </row>
     <row r="89" spans="1:4" x14ac:dyDescent="0.3">
@@ -2165,13 +2165,13 @@
         <v>0.42078300000000002</v>
       </c>
       <c r="B89">
-        <v>11.9169</v>
+        <v>12.029400000000001</v>
       </c>
       <c r="C89">
         <v>0.42078300000000002</v>
       </c>
       <c r="D89">
-        <v>11.9169</v>
+        <v>12.029400000000001</v>
       </c>
     </row>
     <row r="90" spans="1:4" x14ac:dyDescent="0.3">
@@ -2179,13 +2179,13 @@
         <v>0.418605</v>
       </c>
       <c r="B90">
-        <v>10.531700000000001</v>
+        <v>10.814500000000001</v>
       </c>
       <c r="C90">
         <v>0.418605</v>
       </c>
       <c r="D90">
-        <v>10.531700000000001</v>
+        <v>10.814500000000001</v>
       </c>
     </row>
     <row r="91" spans="1:4" x14ac:dyDescent="0.3">
@@ -2193,13 +2193,13 @@
         <v>0.42048099999999999</v>
       </c>
       <c r="B91">
-        <v>10.357100000000001</v>
+        <v>9.9131699999999991</v>
       </c>
       <c r="C91">
         <v>0.42048099999999999</v>
       </c>
       <c r="D91">
-        <v>10.357100000000001</v>
+        <v>9.9131699999999991</v>
       </c>
     </row>
     <row r="92" spans="1:4" x14ac:dyDescent="0.3">
@@ -2207,13 +2207,13 @@
         <v>0.4219</v>
       </c>
       <c r="B92">
-        <v>12.633100000000001</v>
+        <v>9.7222799999999996</v>
       </c>
       <c r="C92">
         <v>0.4219</v>
       </c>
       <c r="D92">
-        <v>12.633100000000001</v>
+        <v>9.7222799999999996</v>
       </c>
     </row>
     <row r="93" spans="1:4" x14ac:dyDescent="0.3">
@@ -2221,13 +2221,13 @@
         <v>0.42053099999999999</v>
       </c>
       <c r="B93">
-        <v>11.939399999999999</v>
+        <v>11.9626</v>
       </c>
       <c r="C93">
         <v>0.42053099999999999</v>
       </c>
       <c r="D93">
-        <v>11.939399999999999</v>
+        <v>11.9626</v>
       </c>
     </row>
     <row r="94" spans="1:4" x14ac:dyDescent="0.3">
@@ -2235,13 +2235,13 @@
         <v>0.42602600000000002</v>
       </c>
       <c r="B94">
-        <v>12.1655</v>
+        <v>12.3283</v>
       </c>
       <c r="C94">
         <v>0.42602600000000002</v>
       </c>
       <c r="D94">
-        <v>12.1655</v>
+        <v>12.3283</v>
       </c>
     </row>
     <row r="95" spans="1:4" x14ac:dyDescent="0.3">
@@ -2249,13 +2249,13 @@
         <v>0.52430600000000005</v>
       </c>
       <c r="B95">
-        <v>11.8269</v>
+        <v>12.516999999999999</v>
       </c>
       <c r="C95">
         <v>0.52430600000000005</v>
       </c>
       <c r="D95">
-        <v>11.8269</v>
+        <v>12.516999999999999</v>
       </c>
     </row>
     <row r="96" spans="1:4" x14ac:dyDescent="0.3">
@@ -2263,13 +2263,13 @@
         <v>0.53110000000000002</v>
       </c>
       <c r="B96">
-        <v>12.247400000000001</v>
+        <v>10.068</v>
       </c>
       <c r="C96">
         <v>0.53110000000000002</v>
       </c>
       <c r="D96">
-        <v>12.247400000000001</v>
+        <v>10.068</v>
       </c>
     </row>
     <row r="97" spans="1:4" x14ac:dyDescent="0.3">
@@ -2277,13 +2277,13 @@
         <v>0.41706199999999999</v>
       </c>
       <c r="B97">
-        <v>10.262</v>
+        <v>12.3354</v>
       </c>
       <c r="C97">
         <v>0.41706199999999999</v>
       </c>
       <c r="D97">
-        <v>10.262</v>
+        <v>12.3354</v>
       </c>
     </row>
     <row r="98" spans="1:4" x14ac:dyDescent="0.3">
@@ -2291,13 +2291,13 @@
         <v>0.32120900000000002</v>
       </c>
       <c r="B98">
-        <v>10.289199999999999</v>
+        <v>12.0337</v>
       </c>
       <c r="C98">
         <v>0.32120900000000002</v>
       </c>
       <c r="D98">
-        <v>10.289199999999999</v>
+        <v>12.0337</v>
       </c>
     </row>
     <row r="99" spans="1:4" x14ac:dyDescent="0.3">
@@ -2305,13 +2305,13 @@
         <v>0.31928600000000001</v>
       </c>
       <c r="B99">
-        <v>12.1988</v>
+        <v>10.1873</v>
       </c>
       <c r="C99">
         <v>0.31928600000000001</v>
       </c>
       <c r="D99">
-        <v>12.1988</v>
+        <v>10.1873</v>
       </c>
     </row>
     <row r="100" spans="1:4" x14ac:dyDescent="0.3">
@@ -2319,13 +2319,13 @@
         <v>0.42218899999999998</v>
       </c>
       <c r="B100">
-        <v>12.2209</v>
+        <v>10.3523</v>
       </c>
       <c r="C100">
         <v>0.42218899999999998</v>
       </c>
       <c r="D100">
-        <v>12.2209</v>
+        <v>10.3523</v>
       </c>
     </row>
     <row r="101" spans="1:4" x14ac:dyDescent="0.3">
@@ -2333,13 +2333,13 @@
         <v>0.31812200000000002</v>
       </c>
       <c r="B101">
-        <v>13.011100000000001</v>
+        <v>12.430999999999999</v>
       </c>
       <c r="C101">
         <v>0.31812200000000002</v>
       </c>
       <c r="D101">
-        <v>13.011100000000001</v>
+        <v>12.430999999999999</v>
       </c>
     </row>
   </sheetData>
